--- a/embeddings/sandbox/blender/plots/df_all_pca_donut.xlsx
+++ b/embeddings/sandbox/blender/plots/df_all_pca_donut.xlsx
@@ -5,16 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="real" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="synthetic_es-digital-seq" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="synthetic_es-digital-line-degra" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="synthetic_es-digital-paragraph-" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="synthetic_es-digital-rotation-d" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="synthetic_es-digital-zoom-degra" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="synthetic_es-render-seq" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="es-digital-seq" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="es-digital-line" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="es-digital-paragraph" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="es-digital-rotation" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="es-digital-zoom" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="es-render-seq" sheetId="7" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="1063">
   <si>
     <t xml:space="preserve">PC1</t>
   </si>
@@ -986,6 +986,9 @@
   </si>
   <si>
     <t xml:space="preserve">es-digital-line-degradation-seq_spanish_monterraso_0807_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
   <si>
     <t xml:space="preserve">es-digital-line-degradation-seq_spanish_deus_0119_0</t>
@@ -3328,7 +3331,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D153"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -5489,7 +5492,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D152"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -7635,10 +7638,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AI280"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="54.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7836,6 +7839,9 @@
       <c r="D14" s="0" t="s">
         <v>319</v>
       </c>
+      <c r="AI14" s="0" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
@@ -7848,7 +7854,7 @@
         <v>1.71911612650428</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7862,7 +7868,7 @@
         <v>1.13693394017356</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7876,7 +7882,7 @@
         <v>1.71401785576953</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7890,7 +7896,7 @@
         <v>1.74008017177337</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7904,7 +7910,7 @@
         <v>1.70066623900923</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7918,7 +7924,7 @@
         <v>1.76531046888706</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7932,7 +7938,7 @@
         <v>1.11909969834937</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7946,7 +7952,7 @@
         <v>1.6280372629524</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7960,7 +7966,7 @@
         <v>0.932667805212203</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7974,7 +7980,7 @@
         <v>1.74197279863255</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7988,7 +7994,7 @@
         <v>1.74796809197295</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8002,7 +8008,7 @@
         <v>0.9110185566087</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8016,7 +8022,7 @@
         <v>1.70789243861172</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8030,7 +8036,7 @@
         <v>1.73368973815876</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8044,7 +8050,7 @@
         <v>1.77416997346348</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8058,7 +8064,7 @@
         <v>1.17064003098497</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8072,7 +8078,7 @@
         <v>1.75934707489493</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8086,7 +8092,7 @@
         <v>1.70879511178279</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8100,7 +8106,7 @@
         <v>1.0143768182649</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8114,7 +8120,7 @@
         <v>1.76563568603574</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8128,7 +8134,7 @@
         <v>1.6349904841935</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8142,7 +8148,7 @@
         <v>1.74436207785607</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8156,7 +8162,7 @@
         <v>1.7599604584205</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8170,7 +8176,7 @@
         <v>1.01802429567561</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8184,7 +8190,7 @@
         <v>1.70402983636061</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8198,7 +8204,7 @@
         <v>1.0990051659371</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8212,7 +8218,7 @@
         <v>1.66199232587754</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8226,7 +8232,7 @@
         <v>1.77076864999024</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8240,7 +8246,7 @@
         <v>0.97409866563305</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8254,7 +8260,7 @@
         <v>0.999401787394278</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8268,7 +8274,7 @@
         <v>1.71451751075718</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8282,7 +8288,7 @@
         <v>1.08747720137205</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8296,7 +8302,7 @@
         <v>1.13941947052445</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8310,7 +8316,7 @@
         <v>1.74670016274251</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8324,7 +8330,7 @@
         <v>1.7596898140274</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8338,7 +8344,7 @@
         <v>1.11622515478393</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8352,7 +8358,7 @@
         <v>1.70623343708454</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8366,7 +8372,7 @@
         <v>1.76297881539299</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8380,7 +8386,7 @@
         <v>1.74863102475978</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8394,7 +8400,7 @@
         <v>1.70997223317992</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8408,7 +8414,7 @@
         <v>1.5995435705222</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8422,7 +8428,7 @@
         <v>1.69073239934384</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8436,7 +8442,7 @@
         <v>1.69651299711548</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8450,7 +8456,7 @@
         <v>1.63328038830821</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8464,7 +8470,7 @@
         <v>1.61471919228175</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8478,7 +8484,7 @@
         <v>1.696034873348</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8492,7 +8498,7 @@
         <v>1.7444895784945</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8506,7 +8512,7 @@
         <v>1.70133968878165</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8520,7 +8526,7 @@
         <v>1.71248856063901</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8534,7 +8540,7 @@
         <v>1.73003521862155</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8548,7 +8554,7 @@
         <v>1.62022587755183</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8562,7 +8568,7 @@
         <v>1.20644022404769</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8576,7 +8582,7 @@
         <v>1.6822408692002</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8590,7 +8596,7 @@
         <v>1.7565900278771</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8604,7 +8610,7 @@
         <v>1.62787510557462</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8618,7 +8624,7 @@
         <v>1.64459473357545</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8632,7 +8638,7 @@
         <v>1.09605522942827</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8646,7 +8652,7 @@
         <v>1.73119424762188</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8660,7 +8666,7 @@
         <v>1.66471316480734</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8674,7 +8680,7 @@
         <v>1.70577252515242</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8688,7 +8694,7 @@
         <v>1.7144600516732</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8702,7 +8708,7 @@
         <v>1.74669614263071</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8716,7 +8722,7 @@
         <v>1.65053451047081</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8730,7 +8736,7 @@
         <v>1.68987524373238</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8744,7 +8750,7 @@
         <v>1.63081357802604</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8758,7 +8764,7 @@
         <v>1.76764893950892</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8772,7 +8778,7 @@
         <v>0.97482209009779</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8786,7 +8792,7 @@
         <v>0.982781660736285</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8800,7 +8806,7 @@
         <v>0.958083055062548</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8814,7 +8820,7 @@
         <v>1.0017571773423</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8828,7 +8834,7 @@
         <v>0.985695959747488</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8842,7 +8848,7 @@
         <v>1.67430847918628</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8856,7 +8862,7 @@
         <v>1.04133067333749</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8870,7 +8876,7 @@
         <v>1.75635972589563</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8884,7 +8890,7 @@
         <v>1.15007052706312</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8898,7 +8904,7 @@
         <v>1.70469215068581</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8912,7 +8918,7 @@
         <v>1.62021982149939</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8926,7 +8932,7 @@
         <v>1.10486528436296</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8940,7 +8946,7 @@
         <v>0.876795779231822</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8954,7 +8960,7 @@
         <v>1.72166489997669</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8968,7 +8974,7 @@
         <v>0.991992484224664</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8982,7 +8988,7 @@
         <v>1.74152053825257</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8996,7 +9002,7 @@
         <v>1.64655332214931</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9010,7 +9016,7 @@
         <v>1.69575077211948</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9024,7 +9030,7 @@
         <v>1.62897924425666</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9038,7 +9044,7 @@
         <v>1.77433990967733</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9052,7 +9058,7 @@
         <v>1.73641141486907</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9066,7 +9072,7 @@
         <v>1.74376081849933</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9080,7 +9086,7 @@
         <v>1.11921239683741</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9094,7 +9100,7 @@
         <v>1.72519728155333</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9108,7 +9114,7 @@
         <v>0.917055066703523</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9122,7 +9128,7 @@
         <v>1.70776556582624</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9136,7 +9142,7 @@
         <v>0.959113170608368</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9150,7 +9156,7 @@
         <v>1.74967742286068</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9164,7 +9170,7 @@
         <v>1.77517751850175</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9178,7 +9184,7 @@
         <v>1.68509545844857</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9192,7 +9198,7 @@
         <v>1.74012062944146</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9206,7 +9212,7 @@
         <v>1.6821891409125</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9220,7 +9226,7 @@
         <v>1.07680277013082</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9234,7 +9240,7 @@
         <v>1.71729707946947</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9248,7 +9254,7 @@
         <v>0.978272064593563</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9262,7 +9268,7 @@
         <v>1.70846646500944</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9276,7 +9282,7 @@
         <v>1.08026883876313</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9290,7 +9296,7 @@
         <v>1.65697782310431</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9304,7 +9310,7 @@
         <v>1.67152605185401</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9318,7 +9324,7 @@
         <v>1.72207150304527</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9332,7 +9338,7 @@
         <v>1.74432223795224</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9346,7 +9352,7 @@
         <v>1.66830036929857</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9360,7 +9366,7 @@
         <v>1.06647140173495</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9374,7 +9380,7 @@
         <v>1.73496682655674</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9388,7 +9394,7 @@
         <v>1.21384381753651</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9402,7 +9408,7 @@
         <v>1.13431797818292</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9416,7 +9422,7 @@
         <v>1.64738148909342</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9430,7 +9436,7 @@
         <v>1.61871077653301</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9444,7 +9450,7 @@
         <v>1.67859783777588</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9458,7 +9464,7 @@
         <v>1.74931489837072</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9472,7 +9478,7 @@
         <v>1.67544956422401</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9486,7 +9492,7 @@
         <v>1.77513864798329</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9500,7 +9506,7 @@
         <v>1.03372397327392</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9514,7 +9520,7 @@
         <v>1.672287355762</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9528,7 +9534,7 @@
         <v>1.70125080241756</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9542,7 +9548,7 @@
         <v>1.70333859394261</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9556,7 +9562,7 @@
         <v>1.75073409384978</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9570,7 +9576,7 @@
         <v>1.74041414030762</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9584,7 +9590,7 @@
         <v>1.71220592395709</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9598,7 +9604,7 @@
         <v>1.6531108565221</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9612,7 +9618,7 @@
         <v>0.900520910051873</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9626,7 +9632,7 @@
         <v>0.915745188495312</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9640,7 +9646,7 @@
         <v>1.67548503665534</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9654,7 +9660,7 @@
         <v>0.903151664447828</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9668,7 +9674,7 @@
         <v>1.65026172481364</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9682,7 +9688,7 @@
         <v>1.69354106000863</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9696,7 +9702,7 @@
         <v>1.70823598958692</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9710,7 +9716,7 @@
         <v>1.67498956044443</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9724,7 +9730,7 @@
         <v>0.977354327537581</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9738,7 +9744,7 @@
         <v>1.6400858606474</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9752,7 +9758,7 @@
         <v>0.898558109114141</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9766,7 +9772,7 @@
         <v>1.66720823737064</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -9914,7 +9920,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D152"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -9941,7 +9947,7 @@
         <v>1.52769061297835</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9955,7 +9961,7 @@
         <v>1.47628342197015</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9969,7 +9975,7 @@
         <v>1.17042403636453</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9983,7 +9989,7 @@
         <v>1.50486703050261</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9997,7 +10003,7 @@
         <v>1.50858153630281</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10011,7 +10017,7 @@
         <v>1.26045167846417</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10025,7 +10031,7 @@
         <v>1.52060117551024</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10039,7 +10045,7 @@
         <v>1.36372305204056</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10053,7 +10059,7 @@
         <v>1.1482433676193</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10067,7 +10073,7 @@
         <v>1.14124908363013</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10081,7 +10087,7 @@
         <v>1.1386607002435</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10095,7 +10101,7 @@
         <v>1.22482525499308</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10109,7 +10115,7 @@
         <v>1.13006840173451</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10123,7 +10129,7 @@
         <v>1.47665863806877</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10137,7 +10143,7 @@
         <v>1.21410437218872</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10151,7 +10157,7 @@
         <v>1.37405393182838</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10165,7 +10171,7 @@
         <v>1.49500681004481</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10179,7 +10185,7 @@
         <v>1.37834655272935</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10193,7 +10199,7 @@
         <v>1.54130884217443</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10207,7 +10213,7 @@
         <v>1.19655066515509</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10221,7 +10227,7 @@
         <v>1.18235166460607</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10235,7 +10241,7 @@
         <v>1.1247012797264</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10249,7 +10255,7 @@
         <v>1.51574559965614</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10263,7 +10269,7 @@
         <v>1.50316349765755</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10277,7 +10283,7 @@
         <v>1.08541623307535</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10291,7 +10297,7 @@
         <v>1.37073992055557</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10305,7 +10311,7 @@
         <v>1.50925914969628</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10319,7 +10325,7 @@
         <v>1.32826649925066</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10333,7 +10339,7 @@
         <v>1.24036339422762</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10347,7 +10353,7 @@
         <v>1.29902472668418</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10361,7 +10367,7 @@
         <v>1.35071278090649</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10375,7 +10381,7 @@
         <v>1.14330819006106</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10389,7 +10395,7 @@
         <v>1.55020391288707</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10403,7 +10409,7 @@
         <v>1.1860072555847</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10417,7 +10423,7 @@
         <v>1.52129662554012</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10431,7 +10437,7 @@
         <v>1.2751585216176</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10445,7 +10451,7 @@
         <v>1.22214239982066</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10459,7 +10465,7 @@
         <v>1.37029059143826</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10473,7 +10479,7 @@
         <v>1.158425899638</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10487,7 +10493,7 @@
         <v>1.21357791491978</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10501,7 +10507,7 @@
         <v>1.28603214708513</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10515,7 +10521,7 @@
         <v>1.10270480504151</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10529,7 +10535,7 @@
         <v>1.10195161028628</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10543,7 +10549,7 @@
         <v>1.45010320053484</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10557,7 +10563,7 @@
         <v>1.1639230022594</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10571,7 +10577,7 @@
         <v>1.22050441220569</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10585,7 +10591,7 @@
         <v>1.50687667499478</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10599,7 +10605,7 @@
         <v>1.52563712853191</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10613,7 +10619,7 @@
         <v>1.20388235023017</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10627,7 +10633,7 @@
         <v>1.45314979855321</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10641,7 +10647,7 @@
         <v>1.3115338928066</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10655,7 +10661,7 @@
         <v>1.52817414574289</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10669,7 +10675,7 @@
         <v>1.37426433482679</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10683,7 +10689,7 @@
         <v>1.10804487475914</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10697,7 +10703,7 @@
         <v>1.44635641445763</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10711,7 +10717,7 @@
         <v>1.47703233887016</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10725,7 +10731,7 @@
         <v>1.48244883475489</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10739,7 +10745,7 @@
         <v>1.45841451466308</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10753,7 +10759,7 @@
         <v>1.50632382944051</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10767,7 +10773,7 @@
         <v>1.52795019508679</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10781,7 +10787,7 @@
         <v>1.45719597879262</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10795,7 +10801,7 @@
         <v>1.45152955096978</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10809,7 +10815,7 @@
         <v>1.45749998889341</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10823,7 +10829,7 @@
         <v>1.46192841721498</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10837,7 +10843,7 @@
         <v>1.2025190919174</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10851,7 +10857,7 @@
         <v>1.46514763349948</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10865,7 +10871,7 @@
         <v>1.54075241787509</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10879,7 +10885,7 @@
         <v>1.43981852689382</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10893,7 +10899,7 @@
         <v>1.16693306719101</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10907,7 +10913,7 @@
         <v>1.16767355023749</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10921,7 +10927,7 @@
         <v>1.5128396572581</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10935,7 +10941,7 @@
         <v>1.21678659897834</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10949,7 +10955,7 @@
         <v>1.52736097988173</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10963,7 +10969,7 @@
         <v>1.45474988420351</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10977,7 +10983,7 @@
         <v>1.52716680623178</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10991,7 +10997,7 @@
         <v>1.1875993336776</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11005,7 +11011,7 @@
         <v>1.49192439723405</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11019,7 +11025,7 @@
         <v>1.14563724443277</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11033,7 +11039,7 @@
         <v>1.31514294948843</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11047,7 +11053,7 @@
         <v>1.13564692126572</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11061,7 +11067,7 @@
         <v>1.1548821949457</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11075,7 +11081,7 @@
         <v>1.13970591398703</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11089,7 +11095,7 @@
         <v>1.15357270441627</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11103,7 +11109,7 @@
         <v>1.1433536096928</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11117,7 +11123,7 @@
         <v>1.2594300595826</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11131,7 +11137,7 @@
         <v>1.12094111337464</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11145,7 +11151,7 @@
         <v>1.51609432419003</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11159,7 +11165,7 @@
         <v>1.22600296154167</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11173,7 +11179,7 @@
         <v>1.46643583600769</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11187,7 +11193,7 @@
         <v>1.47853723264753</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11201,7 +11207,7 @@
         <v>1.18293031641858</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11215,7 +11221,7 @@
         <v>1.08165418885764</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11229,7 +11235,7 @@
         <v>1.37287370429705</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11243,7 +11249,7 @@
         <v>1.08321907370228</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11257,7 +11263,7 @@
         <v>1.50594621123365</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11271,7 +11277,7 @@
         <v>1.17093044831154</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11285,7 +11291,7 @@
         <v>1.3745685737017</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11299,7 +11305,7 @@
         <v>1.48424545393655</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11313,7 +11319,7 @@
         <v>1.33477023728343</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11327,7 +11333,7 @@
         <v>1.42531782100297</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11341,7 +11347,7 @@
         <v>1.51285079803297</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11355,7 +11361,7 @@
         <v>1.20133490618578</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11369,7 +11375,7 @@
         <v>1.46457690284852</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11383,7 +11389,7 @@
         <v>1.1000670032069</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11397,7 +11403,7 @@
         <v>1.5245305565019</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11411,7 +11417,7 @@
         <v>1.10851100992668</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11425,7 +11431,7 @@
         <v>1.51277625835306</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11439,7 +11445,7 @@
         <v>1.34382174055489</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11453,7 +11459,7 @@
         <v>1.45842687518481</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11467,7 +11473,7 @@
         <v>1.49620001950858</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11481,7 +11487,7 @@
         <v>1.39915705851267</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11495,7 +11501,7 @@
         <v>1.18463062159571</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11509,7 +11515,7 @@
         <v>1.55026655199015</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11523,7 +11529,7 @@
         <v>1.12579961190981</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11537,7 +11543,7 @@
         <v>1.36717010722475</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11551,7 +11557,7 @@
         <v>1.18454161798575</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11565,7 +11571,7 @@
         <v>1.21471713959944</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11579,7 +11585,7 @@
         <v>1.22997458963847</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11593,7 +11599,7 @@
         <v>1.38902736069324</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11607,7 +11613,7 @@
         <v>1.49372643744801</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11621,7 +11627,7 @@
         <v>1.39999194607528</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11635,7 +11641,7 @@
         <v>1.1601606234036</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11649,7 +11655,7 @@
         <v>1.48855262441518</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11663,7 +11669,7 @@
         <v>1.23384006999079</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11677,7 +11683,7 @@
         <v>1.19323278052194</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11691,7 +11697,7 @@
         <v>1.20567129218937</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11705,7 +11711,7 @@
         <v>1.46400830158134</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11719,7 +11725,7 @@
         <v>1.25256648270215</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11733,7 +11739,7 @@
         <v>1.51606039779951</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11747,7 +11753,7 @@
         <v>1.27768513044431</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11761,7 +11767,7 @@
         <v>1.3574888722947</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11775,7 +11781,7 @@
         <v>1.12620456093502</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11789,7 +11795,7 @@
         <v>1.41023975551782</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11803,7 +11809,7 @@
         <v>1.46804368227376</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11817,7 +11823,7 @@
         <v>1.51912990093191</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11831,7 +11837,7 @@
         <v>1.50218600828468</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11845,7 +11851,7 @@
         <v>1.29375511027605</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11859,7 +11865,7 @@
         <v>1.46487052088772</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11873,7 +11879,7 @@
         <v>1.25584370285219</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11887,7 +11893,7 @@
         <v>1.10947139154806</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11901,7 +11907,7 @@
         <v>1.09643347021199</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11915,7 +11921,7 @@
         <v>1.25317912276684</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11929,7 +11935,7 @@
         <v>1.11309536947724</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11943,7 +11949,7 @@
         <v>1.1877593105342</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11957,7 +11963,7 @@
         <v>1.36223192503022</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11971,7 +11977,7 @@
         <v>1.54388924872947</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11985,7 +11991,7 @@
         <v>1.23863865852488</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11999,7 +12005,7 @@
         <v>1.13050832406011</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12013,7 +12019,7 @@
         <v>1.20872182233578</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12027,7 +12033,7 @@
         <v>1.07980836153665</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12041,7 +12047,7 @@
         <v>1.2247389745643</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -12061,7 +12067,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D152"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -12088,7 +12094,7 @@
         <v>0.0839366496982343</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12102,7 +12108,7 @@
         <v>-0.00869893833879587</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12116,7 +12122,7 @@
         <v>0.0579051927395029</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12130,7 +12136,7 @@
         <v>0.0790888531378537</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12144,7 +12150,7 @@
         <v>0.154395246640918</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12158,7 +12164,7 @@
         <v>0.22915222096632</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12172,7 +12178,7 @@
         <v>-0.0403780885657565</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12186,7 +12192,7 @@
         <v>0.0772448582180658</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12200,7 +12206,7 @@
         <v>-0.182941471812643</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12214,7 +12220,7 @@
         <v>-0.437416934734972</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12228,7 +12234,7 @@
         <v>0.00880303197845889</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12242,7 +12248,7 @@
         <v>-0.109115047006543</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12256,7 +12262,7 @@
         <v>-0.44863835190524</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12270,7 +12276,7 @@
         <v>-0.199199672624861</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12284,7 +12290,7 @@
         <v>0.0875779492179185</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12298,7 +12304,7 @@
         <v>0.0200833515871905</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12312,7 +12318,7 @@
         <v>0.0234660369510613</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12326,7 +12332,7 @@
         <v>0.227700914476737</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12340,7 +12346,7 @@
         <v>0.119895934078297</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12354,7 +12360,7 @@
         <v>0.0447243667155499</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12368,7 +12374,7 @@
         <v>0.271263513014373</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12382,7 +12388,7 @@
         <v>0.0827519424716434</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12396,7 +12402,7 @@
         <v>-0.508526105684089</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12410,7 +12416,7 @@
         <v>0.0361219885164843</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12424,7 +12430,7 @@
         <v>0.141441001353313</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12438,7 +12444,7 @@
         <v>0.257882935874399</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12452,7 +12458,7 @@
         <v>0.15045191199215</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12466,7 +12472,7 @@
         <v>0.21061749598546</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12480,7 +12486,7 @@
         <v>-0.183288062155424</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12494,7 +12500,7 @@
         <v>0.0306149800115865</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12508,7 +12514,7 @@
         <v>0.261771786295812</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12522,7 +12528,7 @@
         <v>0.0901702106589632</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12536,7 +12542,7 @@
         <v>0.225203793300831</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12550,7 +12556,7 @@
         <v>0.142109545414311</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12564,7 +12570,7 @@
         <v>0.186924419523514</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12578,7 +12584,7 @@
         <v>0.306875726605147</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12592,7 +12598,7 @@
         <v>0.146969088175518</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12606,7 +12612,7 @@
         <v>0.10734219796978</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12620,7 +12626,7 @@
         <v>0.034596176805965</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12634,7 +12640,7 @@
         <v>0.13358987573135</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12648,7 +12654,7 @@
         <v>0.112927369285667</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12662,7 +12668,7 @@
         <v>0.144824743866334</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12676,7 +12682,7 @@
         <v>0.122237593503891</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12690,7 +12696,7 @@
         <v>0.110625256668494</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12704,7 +12710,7 @@
         <v>0.0839925747571986</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12718,7 +12724,7 @@
         <v>0.216109124783569</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12732,7 +12738,7 @@
         <v>-0.14428914030863</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12746,7 +12752,7 @@
         <v>-0.133313511076916</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12760,7 +12766,7 @@
         <v>0.0188205109411692</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12774,7 +12780,7 @@
         <v>-0.238257427609892</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12788,7 +12794,7 @@
         <v>0.316159803009427</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12802,7 +12808,7 @@
         <v>0.0222130543150216</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12816,7 +12822,7 @@
         <v>0.150890635161354</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12830,7 +12836,7 @@
         <v>-0.0807766879139513</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12844,7 +12850,7 @@
         <v>-0.0346957169659032</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12858,7 +12864,7 @@
         <v>0.0861635938875214</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12872,7 +12878,7 @@
         <v>-0.0611248827417747</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12886,7 +12892,7 @@
         <v>-0.0222764300578104</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12900,7 +12906,7 @@
         <v>0.259016606425221</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12914,7 +12920,7 @@
         <v>-0.0131726270494457</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12928,7 +12934,7 @@
         <v>0.00972241492087234</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12942,7 +12948,7 @@
         <v>0.224717555023522</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12956,7 +12962,7 @@
         <v>0.104906128326532</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12970,7 +12976,7 @@
         <v>0.0902113866039507</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12984,7 +12990,7 @@
         <v>0.163703525632671</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12998,7 +13004,7 @@
         <v>0.0171784161696067</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13012,7 +13018,7 @@
         <v>-0.226385033537037</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13026,7 +13032,7 @@
         <v>-0.112242975726803</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13040,7 +13046,7 @@
         <v>0.0673833245100624</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13054,7 +13060,7 @@
         <v>0.102129235654179</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13068,7 +13074,7 @@
         <v>0.175986042389179</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13082,7 +13088,7 @@
         <v>0.286569881202613</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13096,7 +13102,7 @@
         <v>0.190428279673959</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13110,7 +13116,7 @@
         <v>0.131342014953312</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13124,7 +13130,7 @@
         <v>-0.491221991024345</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13138,7 +13144,7 @@
         <v>-0.252616397478179</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13152,7 +13158,7 @@
         <v>-0.0501264871957852</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13166,7 +13172,7 @@
         <v>-0.0204254630543463</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13180,7 +13186,7 @@
         <v>-0.503856851180142</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13194,7 +13200,7 @@
         <v>-0.125601612848831</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13208,7 +13214,7 @@
         <v>0.196379439953293</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13222,7 +13228,7 @@
         <v>0.0505432825038432</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13236,7 +13242,7 @@
         <v>-0.205449094024819</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13250,7 +13256,7 @@
         <v>0.208923290618584</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13264,7 +13270,7 @@
         <v>0.0374963691285268</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13278,7 +13284,7 @@
         <v>-0.24577358757257</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13292,7 +13298,7 @@
         <v>0.0505965369438899</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13306,7 +13312,7 @@
         <v>0.163499446868209</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13320,7 +13326,7 @@
         <v>0.163455152311994</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13334,7 +13340,7 @@
         <v>-0.176499358921747</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13348,7 +13354,7 @@
         <v>0.0489870727740898</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13362,7 +13368,7 @@
         <v>-0.0347443048958001</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13376,7 +13382,7 @@
         <v>-0.119494716152482</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13390,7 +13396,7 @@
         <v>-0.0751707690255148</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13404,7 +13410,7 @@
         <v>-0.207187799529111</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13418,7 +13424,7 @@
         <v>0.0448376773434278</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13432,7 +13438,7 @@
         <v>0.112761880721075</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13446,7 +13452,7 @@
         <v>0.0244993895119183</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13460,7 +13466,7 @@
         <v>-0.485861269852487</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13474,7 +13480,7 @@
         <v>0.0396450717482524</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13488,7 +13494,7 @@
         <v>0.0194323444361948</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13502,7 +13508,7 @@
         <v>-0.0331366937159623</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13516,7 +13522,7 @@
         <v>-0.027043418161623</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13530,7 +13536,7 @@
         <v>0.0375646665791423</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13544,7 +13550,7 @@
         <v>-0.27315527659648</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13558,7 +13564,7 @@
         <v>0.0525616450216511</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13572,7 +13578,7 @@
         <v>-0.0721251533473004</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13586,7 +13592,7 @@
         <v>0.271768500327897</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13600,7 +13606,7 @@
         <v>0.131100623608148</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13614,7 +13620,7 @@
         <v>0.0222895892506654</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13628,7 +13634,7 @@
         <v>0.0368386400527321</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13642,7 +13648,7 @@
         <v>-0.504187524899341</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13656,7 +13662,7 @@
         <v>0.074433752569588</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13670,7 +13676,7 @@
         <v>0.0728763634866168</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13684,7 +13690,7 @@
         <v>0.099778155717178</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13698,7 +13704,7 @@
         <v>-0.0542966627013137</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13712,7 +13718,7 @@
         <v>-0.150425926122967</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13726,7 +13732,7 @@
         <v>0.0527833698119755</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13740,7 +13746,7 @@
         <v>-0.0976289963792023</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13754,7 +13760,7 @@
         <v>0.185370130300836</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13768,7 +13774,7 @@
         <v>0.0974039208955388</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13782,7 +13788,7 @@
         <v>-0.0267453352322913</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13796,7 +13802,7 @@
         <v>0.0149890620475794</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13810,7 +13816,7 @@
         <v>-0.0131865891292393</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13824,7 +13830,7 @@
         <v>0.162555112085942</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13838,7 +13844,7 @@
         <v>0.0778505008128434</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13852,7 +13858,7 @@
         <v>-0.00299079140364089</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13866,7 +13872,7 @@
         <v>0.183504093783619</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13880,7 +13886,7 @@
         <v>0.0332560072827808</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13894,7 +13900,7 @@
         <v>-0.375022875408886</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13908,7 +13914,7 @@
         <v>0.321248587926045</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13922,7 +13928,7 @@
         <v>-0.455546656442693</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13936,7 +13942,7 @@
         <v>0.315377208065267</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13950,7 +13956,7 @@
         <v>-0.209083004654056</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13964,7 +13970,7 @@
         <v>0.0891650409949709</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13978,7 +13984,7 @@
         <v>0.220129303929884</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13992,7 +13998,7 @@
         <v>-0.0176614985094972</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14006,7 +14012,7 @@
         <v>-0.646206756303935</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14020,7 +14026,7 @@
         <v>0.00675328667980857</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14034,7 +14040,7 @@
         <v>0.341038162583009</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14048,7 +14054,7 @@
         <v>-0.200227676410265</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14062,7 +14068,7 @@
         <v>-0.134923176421633</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14076,7 +14082,7 @@
         <v>-0.219192643631471</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14090,7 +14096,7 @@
         <v>-0.159204510900342</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14104,7 +14110,7 @@
         <v>-0.103236268862018</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14118,7 +14124,7 @@
         <v>0.138436531072181</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14132,7 +14138,7 @@
         <v>0.0931695259161342</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14146,7 +14152,7 @@
         <v>0.378880547717528</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14160,7 +14166,7 @@
         <v>-0.0901077468371807</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14174,7 +14180,7 @@
         <v>0.0692168644404174</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14188,7 +14194,7 @@
         <v>0.254702928484969</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
   </sheetData>
@@ -14208,7 +14214,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D152"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -14235,7 +14241,7 @@
         <v>0.170935464538175</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14249,7 +14255,7 @@
         <v>0.140561904154691</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14263,7 +14269,7 @@
         <v>-0.0529250526776059</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14277,7 +14283,7 @@
         <v>0.216688911245784</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14291,7 +14297,7 @@
         <v>0.311130365998758</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14305,7 +14311,7 @@
         <v>0.00760677481571071</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14319,7 +14325,7 @@
         <v>0.278435194350726</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14333,7 +14339,7 @@
         <v>0.232389790698701</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14347,7 +14353,7 @@
         <v>0.275550948095661</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14361,7 +14367,7 @@
         <v>-0.55940841162341</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14375,7 +14381,7 @@
         <v>1.01852668049374</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14389,7 +14395,7 @@
         <v>0.36452163459274</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14403,7 +14409,7 @@
         <v>-0.363825814068069</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14417,7 +14423,7 @@
         <v>0.0910022948800791</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14431,7 +14437,7 @@
         <v>0.762418543854046</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14445,7 +14451,7 @@
         <v>0.0945086825315169</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14459,7 +14465,7 @@
         <v>0.806508596699486</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14473,7 +14479,7 @@
         <v>0.168959006843661</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14487,7 +14493,7 @@
         <v>0.541791403097672</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14501,7 +14507,7 @@
         <v>0.580339935002321</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14515,7 +14521,7 @@
         <v>0.187151179940105</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14529,7 +14535,7 @@
         <v>0.832698973973426</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14543,7 +14549,7 @@
         <v>0.309596448308643</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14557,7 +14563,7 @@
         <v>0.704091423812419</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14571,7 +14577,7 @@
         <v>0.603535859512727</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14585,7 +14591,7 @@
         <v>0.20721895311737</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14599,7 +14605,7 @@
         <v>0.209667439590368</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14613,7 +14619,7 @@
         <v>0.171761661324385</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14627,7 +14633,7 @@
         <v>0.135574030821132</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14641,7 +14647,7 @@
         <v>0.0195096931042715</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14655,7 +14661,7 @@
         <v>0.366689805783614</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14669,7 +14675,7 @@
         <v>0.695219905745821</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14683,7 +14689,7 @@
         <v>0.756308854574438</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14697,7 +14703,7 @@
         <v>0.245102234577474</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14711,7 +14717,7 @@
         <v>0.739845683042125</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14725,7 +14731,7 @@
         <v>0.271007709868063</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14739,7 +14745,7 @@
         <v>0.250869556450569</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14753,7 +14759,7 @@
         <v>0.426479417414273</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14767,7 +14773,7 @@
         <v>0.0718917488514625</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14781,7 +14787,7 @@
         <v>0.0198829267163179</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14795,7 +14801,7 @@
         <v>0.222687039351386</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14809,7 +14815,7 @@
         <v>0.456148894286935</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14823,7 +14829,7 @@
         <v>0.234425910359603</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14837,7 +14843,7 @@
         <v>0.536079851961512</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14851,7 +14857,7 @@
         <v>0.392425689704959</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14865,7 +14871,7 @@
         <v>0.193211101113071</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14879,7 +14885,7 @@
         <v>-0.0481248550241813</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14893,7 +14899,7 @@
         <v>0.08038721558593</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14907,7 +14913,7 @@
         <v>-0.00148155955238583</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14921,7 +14927,7 @@
         <v>0.438519994192173</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14935,7 +14941,7 @@
         <v>0.0607317187307479</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14949,7 +14955,7 @@
         <v>0.124876396962425</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14963,7 +14969,7 @@
         <v>0.56502467151258</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14977,7 +14983,7 @@
         <v>-0.137830178079721</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14991,7 +14997,7 @@
         <v>0.0445898575163248</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15005,7 +15011,7 @@
         <v>0.425343278449293</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15019,7 +15025,7 @@
         <v>0.205715357182782</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15033,7 +15039,7 @@
         <v>-0.0564139315986907</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15047,7 +15053,7 @@
         <v>0.92711829804643</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15061,7 +15067,7 @@
         <v>0.735945862835204</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15075,7 +15081,7 @@
         <v>0.274765684945903</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15089,7 +15095,7 @@
         <v>0.16377683606385</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15103,7 +15109,7 @@
         <v>0.426778245131386</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15117,7 +15123,7 @@
         <v>0.190028943684165</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15131,7 +15137,7 @@
         <v>0.170586509291068</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15145,7 +15151,7 @@
         <v>0.120277343424595</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15159,7 +15165,7 @@
         <v>0.0630951191493501</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15173,7 +15179,7 @@
         <v>0.71761816879185</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15187,7 +15193,7 @@
         <v>0.129425023143127</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15201,7 +15207,7 @@
         <v>0.148558403246675</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15215,7 +15221,7 @@
         <v>0.929185984927727</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15229,7 +15235,7 @@
         <v>0.902374604997933</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15243,7 +15249,7 @@
         <v>-0.00922140464956245</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15257,7 +15263,7 @@
         <v>0.547557248935804</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15271,7 +15277,7 @@
         <v>-0.284076633132254</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15285,7 +15291,7 @@
         <v>-0.356927063445685</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15299,7 +15305,7 @@
         <v>0.00748333405622104</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15313,7 +15319,7 @@
         <v>-0.0213616964588228</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15327,7 +15333,7 @@
         <v>0.477078185247965</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15341,7 +15347,7 @@
         <v>0.151004550812927</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15355,7 +15361,7 @@
         <v>0.65484246221657</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15369,7 +15375,7 @@
         <v>0.314877724131374</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15383,7 +15389,7 @@
         <v>0.0760155663747031</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15397,7 +15403,7 @@
         <v>0.167045568883039</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15411,7 +15417,7 @@
         <v>0.160342750236829</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15425,7 +15431,7 @@
         <v>-0.404596062479879</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15439,7 +15445,7 @@
         <v>0.53225861971064</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15453,7 +15459,7 @@
         <v>0.26915036778394</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15467,7 +15473,7 @@
         <v>0.214203530619929</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15481,7 +15487,7 @@
         <v>-0.0831315831422037</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15495,7 +15501,7 @@
         <v>0.0289042262953285</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15509,7 +15515,7 @@
         <v>0.1021976035067</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15523,7 +15529,7 @@
         <v>-0.154390153230183</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15537,7 +15543,7 @@
         <v>0.142513891171854</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15551,7 +15557,7 @@
         <v>0.407417731556188</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15565,7 +15571,7 @@
         <v>0.055658249070345</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15579,7 +15585,7 @@
         <v>0.476244647276752</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15593,7 +15599,7 @@
         <v>0.113673198618595</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15607,7 +15613,7 @@
         <v>0.389871427075755</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15621,7 +15627,7 @@
         <v>0.493395449484976</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15635,7 +15641,7 @@
         <v>0.622331300639921</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15649,7 +15655,7 @@
         <v>-0.0596105915113516</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15663,7 +15669,7 @@
         <v>0.264213877844056</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15677,7 +15683,7 @@
         <v>0.729255554393893</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15691,7 +15697,7 @@
         <v>-0.0433006887594831</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15705,7 +15711,7 @@
         <v>0.0633285520522491</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15719,7 +15725,7 @@
         <v>0.226647133512915</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15733,7 +15739,7 @@
         <v>0.856225645653366</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15747,7 +15753,7 @@
         <v>0.630975604167639</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15761,7 +15767,7 @@
         <v>0.17571160363104</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15775,7 +15781,7 @@
         <v>0.0254892456497506</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15789,7 +15795,7 @@
         <v>-0.118060689168765</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15803,7 +15809,7 @@
         <v>0.121702105233924</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15817,7 +15823,7 @@
         <v>0.144902018891136</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15831,7 +15837,7 @@
         <v>0.0765646761757739</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15845,7 +15851,7 @@
         <v>-0.109268382071237</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15859,7 +15865,7 @@
         <v>0.0412758778858593</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15873,7 +15879,7 @@
         <v>0.691996745223902</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15887,7 +15893,7 @@
         <v>0.125636764248662</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15901,7 +15907,7 @@
         <v>0.345494593751032</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15915,7 +15921,7 @@
         <v>0.0890383218423012</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15929,7 +15935,7 @@
         <v>0.220945685900745</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15943,7 +15949,7 @@
         <v>0.213548553017911</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15957,7 +15963,7 @@
         <v>0.158135918034843</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15971,7 +15977,7 @@
         <v>0.0242377959809845</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15985,7 +15991,7 @@
         <v>0.645080940354311</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15999,7 +16005,7 @@
         <v>0.667152395230379</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16013,7 +16019,7 @@
         <v>0.213341896064941</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16027,7 +16033,7 @@
         <v>0.604965831412846</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16041,7 +16047,7 @@
         <v>0.471336339347561</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16055,7 +16061,7 @@
         <v>0.248337413814649</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16069,7 +16075,7 @@
         <v>-0.281583443630094</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16083,7 +16089,7 @@
         <v>0.654910518060651</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16097,7 +16103,7 @@
         <v>-0.185456502162648</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16111,7 +16117,7 @@
         <v>0.0906284505014674</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16125,7 +16131,7 @@
         <v>0.253956656998888</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16139,7 +16145,7 @@
         <v>0.974661244386159</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16153,7 +16159,7 @@
         <v>-0.421145495082232</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16167,7 +16173,7 @@
         <v>0.0632786571225124</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16181,7 +16187,7 @@
         <v>0.118664452863048</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16195,7 +16201,7 @@
         <v>0.443105738347552</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16209,7 +16215,7 @@
         <v>0.107610700830437</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16223,7 +16229,7 @@
         <v>-0.404735471119048</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16237,7 +16243,7 @@
         <v>-0.112592574647039</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16251,7 +16257,7 @@
         <v>0.467768675609332</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16265,7 +16271,7 @@
         <v>0.137677301255648</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16279,7 +16285,7 @@
         <v>0.0827097373690231</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16293,7 +16299,7 @@
         <v>0.858814598152193</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16307,7 +16313,7 @@
         <v>0.28639088034824</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16321,7 +16327,7 @@
         <v>0.82524835443479</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16335,7 +16341,7 @@
         <v>0.909362174629182</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
   </sheetData>
@@ -16355,7 +16361,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D152"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -16382,7 +16388,7 @@
         <v>-0.200165450814088</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16396,7 +16402,7 @@
         <v>-0.408770922400464</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16410,7 +16416,7 @@
         <v>0.182419717537996</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16424,7 +16430,7 @@
         <v>-0.570638137685341</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16438,7 +16444,7 @@
         <v>0.0666154908581955</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16452,7 +16458,7 @@
         <v>-0.310191428650502</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16466,7 +16472,7 @@
         <v>0.0676691640001246</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16480,7 +16486,7 @@
         <v>-0.714203746270679</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16494,7 +16500,7 @@
         <v>-0.258570085545279</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16508,7 +16514,7 @@
         <v>0.0664821262542645</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16522,7 +16528,7 @@
         <v>-0.149764009911621</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16536,7 +16542,7 @@
         <v>-0.0243978005392522</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16550,7 +16556,7 @@
         <v>-0.395190390766018</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16564,7 +16570,7 @@
         <v>-0.536946588200533</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16578,7 +16584,7 @@
         <v>-0.673811711804384</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16592,7 +16598,7 @@
         <v>-0.0927464408357828</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16606,7 +16612,7 @@
         <v>-0.807138861747349</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16620,7 +16626,7 @@
         <v>-0.385683984115364</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16634,7 +16640,7 @@
         <v>-0.201481175872571</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16648,7 +16654,7 @@
         <v>-0.430258985992997</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16662,7 +16668,7 @@
         <v>-0.252126395931522</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16676,7 +16682,7 @@
         <v>-0.794338110570295</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16690,7 +16696,7 @@
         <v>-0.17388013026258</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16704,7 +16710,7 @@
         <v>-0.798572029098155</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16718,7 +16724,7 @@
         <v>-0.231711339658373</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16732,7 +16738,7 @@
         <v>0.087476509347153</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16746,7 +16752,7 @@
         <v>-0.0561868064362527</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16760,7 +16766,7 @@
         <v>-0.175525420038718</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16774,7 +16780,7 @@
         <v>-0.359885329802944</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16788,7 +16794,7 @@
         <v>-0.0594210488710005</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16802,7 +16808,7 @@
         <v>-0.179749344288644</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16816,7 +16822,7 @@
         <v>-0.0416437953006161</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16830,7 +16836,7 @@
         <v>-0.124601631153054</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16844,7 +16850,7 @@
         <v>-0.19237420307364</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16858,7 +16864,7 @@
         <v>0.206917512759654</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16872,7 +16878,7 @@
         <v>0.0864104650255744</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16886,7 +16892,7 @@
         <v>-0.767935769872932</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16900,7 +16906,7 @@
         <v>-0.33449729923782</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16914,7 +16920,7 @@
         <v>-0.207372913161959</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16928,7 +16934,7 @@
         <v>-0.0208243424636745</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16942,7 +16948,7 @@
         <v>-0.0110556916626261</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16956,7 +16962,7 @@
         <v>-0.148840558741626</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16970,7 +16976,7 @@
         <v>0.155539998561766</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16984,7 +16990,7 @@
         <v>-0.219121012173273</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16998,7 +17004,7 @@
         <v>0.031904805505822</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17012,7 +17018,7 @@
         <v>-0.869613357759173</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17026,7 +17032,7 @@
         <v>-0.0438359735256531</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17040,7 +17046,7 @@
         <v>-0.324788360974687</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17054,7 +17060,7 @@
         <v>-0.708851371571157</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17068,7 +17074,7 @@
         <v>0.0302384256828261</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17082,7 +17088,7 @@
         <v>-0.287084709723648</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17096,7 +17102,7 @@
         <v>-0.271496336347369</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17110,7 +17116,7 @@
         <v>-0.44373637771038</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17124,7 +17130,7 @@
         <v>-0.0855428800770599</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17138,7 +17144,7 @@
         <v>-0.172589104865215</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17152,7 +17158,7 @@
         <v>-0.266139794556598</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17166,7 +17172,7 @@
         <v>-0.425582361913401</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17180,7 +17186,7 @@
         <v>-0.0809688775679107</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17194,7 +17200,7 @@
         <v>-0.0223282658098793</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17208,7 +17214,7 @@
         <v>-0.452233460845132</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17222,7 +17228,7 @@
         <v>-0.073593491619651</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17236,7 +17242,7 @@
         <v>0.215537067399993</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17250,7 +17256,7 @@
         <v>-0.676720840626727</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17264,7 +17270,7 @@
         <v>-0.328709839237778</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17278,7 +17284,7 @@
         <v>-0.443224242957927</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17292,7 +17298,7 @@
         <v>-0.0125767097182634</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17306,7 +17312,7 @@
         <v>-0.16146505383543</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17320,7 +17326,7 @@
         <v>-0.127322357428383</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17334,7 +17340,7 @@
         <v>-0.35931559519511</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17348,7 +17354,7 @@
         <v>-0.0766394169845941</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17362,7 +17368,7 @@
         <v>-0.571804012683645</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17376,7 +17382,7 @@
         <v>-0.671650077889774</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17390,7 +17396,7 @@
         <v>0.00258320853503946</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17404,7 +17410,7 @@
         <v>-0.0331867122962732</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17418,7 +17424,7 @@
         <v>-0.0287056582742</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17432,7 +17438,7 @@
         <v>-0.555317209193374</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17446,7 +17452,7 @@
         <v>-0.0986801530705619</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17460,7 +17466,7 @@
         <v>-0.489779293213613</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17474,7 +17480,7 @@
         <v>-0.217808287919066</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17488,7 +17494,7 @@
         <v>-0.0294366595803672</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17502,7 +17508,7 @@
         <v>-0.399170250379359</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17516,7 +17522,7 @@
         <v>0.135670489801322</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17530,7 +17536,7 @@
         <v>-0.0610916466951288</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17544,7 +17550,7 @@
         <v>-0.220435045205765</v>
       </c>
       <c r="D85" s="0" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17558,7 +17564,7 @@
         <v>-0.0187391314281609</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17572,7 +17578,7 @@
         <v>-0.538367503252485</v>
       </c>
       <c r="D87" s="0" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17586,7 +17592,7 @@
         <v>-0.828363370749439</v>
       </c>
       <c r="D88" s="0" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17600,7 +17606,7 @@
         <v>0.0886523595425728</v>
       </c>
       <c r="D89" s="0" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17614,7 +17620,7 @@
         <v>-0.3634240554885</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17628,7 +17634,7 @@
         <v>-0.0643329057341378</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17642,7 +17648,7 @@
         <v>0.0926677696615857</v>
       </c>
       <c r="D92" s="0" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17656,7 +17662,7 @@
         <v>0.0244166668884618</v>
       </c>
       <c r="D93" s="0" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17670,7 +17676,7 @@
         <v>-0.250771576223561</v>
       </c>
       <c r="D94" s="0" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17684,7 +17690,7 @@
         <v>-0.305492616369701</v>
       </c>
       <c r="D95" s="0" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17698,7 +17704,7 @@
         <v>-0.279709888515081</v>
       </c>
       <c r="D96" s="0" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17712,7 +17718,7 @@
         <v>-0.106897028676365</v>
       </c>
       <c r="D97" s="0" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17726,7 +17732,7 @@
         <v>-0.562420187412113</v>
       </c>
       <c r="D98" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17740,7 +17746,7 @@
         <v>-0.190986644672121</v>
       </c>
       <c r="D99" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17754,7 +17760,7 @@
         <v>-0.385579690129612</v>
       </c>
       <c r="D100" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17768,7 +17774,7 @@
         <v>-0.147686854793541</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17782,7 +17788,7 @@
         <v>-0.113753715210992</v>
       </c>
       <c r="D102" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17796,7 +17802,7 @@
         <v>-0.779320352677445</v>
       </c>
       <c r="D103" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17810,7 +17816,7 @@
         <v>-0.365474049659636</v>
       </c>
       <c r="D104" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17824,7 +17830,7 @@
         <v>-0.031026908066722</v>
       </c>
       <c r="D105" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17838,7 +17844,7 @@
         <v>-0.192592957277496</v>
       </c>
       <c r="D106" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17852,7 +17858,7 @@
         <v>0.0166252479676676</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17866,7 +17872,7 @@
         <v>0.0475911917369793</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17880,7 +17886,7 @@
         <v>0.209829820620851</v>
       </c>
       <c r="D109" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17894,7 +17900,7 @@
         <v>-0.462915337865969</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17908,7 +17914,7 @@
         <v>0.196817334587062</v>
       </c>
       <c r="D111" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17922,7 +17928,7 @@
         <v>-0.139192201689709</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17936,7 +17942,7 @@
         <v>-0.263215592777712</v>
       </c>
       <c r="D113" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17950,7 +17956,7 @@
         <v>-0.757663827755694</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17964,7 +17970,7 @@
         <v>0.0244899434751389</v>
       </c>
       <c r="D115" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17978,7 +17984,7 @@
         <v>0.127450934533955</v>
       </c>
       <c r="D116" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17992,7 +17998,7 @@
         <v>0.111579489469286</v>
       </c>
       <c r="D117" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18006,7 +18012,7 @@
         <v>-0.645263563084352</v>
       </c>
       <c r="D118" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18020,7 +18026,7 @@
         <v>0.00970320403432323</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18034,7 +18040,7 @@
         <v>-1.06421377553116</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18048,7 +18054,7 @@
         <v>-0.205298269833369</v>
       </c>
       <c r="D121" s="0" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18062,7 +18068,7 @@
         <v>-0.387581966125001</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18076,7 +18082,7 @@
         <v>-0.199212425797764</v>
       </c>
       <c r="D123" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18090,7 +18096,7 @@
         <v>0.0069926888714571</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18104,7 +18110,7 @@
         <v>-0.4683571441807</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18118,7 +18124,7 @@
         <v>-0.713790659358915</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18132,7 +18138,7 @@
         <v>0.193235169201335</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18146,7 +18152,7 @@
         <v>-0.263611838452722</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18160,7 +18166,7 @@
         <v>-0.184815521688946</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18174,7 +18180,7 @@
         <v>-0.219728858979331</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18188,7 +18194,7 @@
         <v>-0.100525568470729</v>
       </c>
       <c r="D131" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18202,7 +18208,7 @@
         <v>-0.194114271592091</v>
       </c>
       <c r="D132" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18216,7 +18222,7 @@
         <v>-0.139308195272767</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18230,7 +18236,7 @@
         <v>-0.101006948593255</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18244,7 +18250,7 @@
         <v>-0.324059060533698</v>
       </c>
       <c r="D135" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18258,7 +18264,7 @@
         <v>-0.127442691344538</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18272,7 +18278,7 @@
         <v>-0.545871218615237</v>
       </c>
       <c r="D137" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18286,7 +18292,7 @@
         <v>-0.0433025386229233</v>
       </c>
       <c r="D138" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18300,7 +18306,7 @@
         <v>0.131115825972429</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18314,7 +18320,7 @@
         <v>-0.721710003965998</v>
       </c>
       <c r="D140" s="0" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18328,7 +18334,7 @@
         <v>0.129254450149653</v>
       </c>
       <c r="D141" s="0" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18342,7 +18348,7 @@
         <v>-0.502754441588327</v>
       </c>
       <c r="D142" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18356,7 +18362,7 @@
         <v>-0.700151940991114</v>
       </c>
       <c r="D143" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18370,7 +18376,7 @@
         <v>-0.39933924989617</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18384,7 +18390,7 @@
         <v>-0.780786746983444</v>
       </c>
       <c r="D145" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18398,7 +18404,7 @@
         <v>0.0380873287821224</v>
       </c>
       <c r="D146" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18412,7 +18418,7 @@
         <v>-1.20306203212078</v>
       </c>
       <c r="D147" s="0" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18426,7 +18432,7 @@
         <v>-0.0204672382446636</v>
       </c>
       <c r="D148" s="0" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18440,7 +18446,7 @@
         <v>-0.050123480406238</v>
       </c>
       <c r="D149" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18454,7 +18460,7 @@
         <v>-0.731187593842091</v>
       </c>
       <c r="D150" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18468,7 +18474,7 @@
         <v>-0.0920223756348713</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18482,7 +18488,7 @@
         <v>-0.217580836853259</v>
       </c>
       <c r="D152" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
   </sheetData>

--- a/embeddings/sandbox/blender/plots/df_all_pca_donut.xlsx
+++ b/embeddings/sandbox/blender/plots/df_all_pca_donut.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="real" sheetId="1" state="visible" r:id="rId2"/>
@@ -952,10 +952,10 @@
     <t xml:space="preserve">es-digital-line-degradation-seq_spanish_liceo_0616_0</t>
   </si>
   <si>
-    <t xml:space="preserve">es-digital-line-degradation-seq_spanish_liceo_0616_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">es-digital-line-degradation-seq_spanish_liceo_0616_2</t>
+    <t xml:space="preserve">es-digital-line-degradation-seq_spanish_patria_0174_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">es-digital-line-degradation-seq_spanish_liceo_0282_2</t>
   </si>
   <si>
     <t xml:space="preserve">es-digital-line-degradation-seq_spanish_liceo_0384_1</t>
@@ -5493,6 +5493,9 @@
   </sheetPr>
   <dimension ref="A1:D152"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34.79"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -7641,7 +7644,7 @@
   <dimension ref="A1:AI280"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="54.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9921,6 +9924,9 @@
   </sheetPr>
   <dimension ref="A1:D152"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="53.47"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -16362,6 +16368,9 @@
   </sheetPr>
   <dimension ref="A1:D152"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50.92"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
